--- a/RACP Data/2020_RACP.xlsx
+++ b/RACP Data/2020_RACP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/RACP Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/racp_sector_classifer/RACP Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{EA0A3438-EBD3-4C00-88E9-A1C3AC7889AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08796686-0F86-4690-BCA9-0451C6434EFF}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{EA0A3438-EBD3-4C00-88E9-A1C3AC7889AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E5C89B4-BB19-40C6-8A19-5854368E7A6C}"/>
   <bookViews>
-    <workbookView xWindow="-28635" yWindow="-13050" windowWidth="28770" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019 RACP Awards" sheetId="2" r:id="rId1"/>
@@ -7722,16 +7722,6 @@
     <t>JASTECH Development Services, Inc</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>The Overbrook Farmacy is situated on a former supermarket that closed in the 1980s. The transit accessible center will bring back the vacant site into productive uses for an underserved community. The existing, crumbling structures at the site will be demolished to construct the newly built center. The center's plans includes required spaces for exam rooms, staff offices, and other requirements such as providing a separate entrance to the wellness center and privacy issues based on HIPPA. Further, the center will include a public venue area that could be offered for educational sessions, event rental, vertical interior agriculture center, a farmer's market, the commercial kitchen, and fresh food market.</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Overbrook School for the Blind Student Accessibility </t>
   </si>
   <si>
@@ -9933,6 +9923,9 @@
       </rPr>
       <t xml:space="preserve"> Township</t>
     </r>
+  </si>
+  <si>
+    <t>The Overbrook Farmacy is situated on a former supermarket that closed in the 1980s. The transit accessible center will bring back the vacant site into productive uses for an underserved community. The existing, crumbling structures at the site will be demolished to construct the newly built center. The center's plans includes required spaces for exam rooms, staff offices, and other requirements such as providing a separate entrance to the wellness center and privacy issues based on HIPPA. Further, the center will include a public venue area that could be offered for educational sessions, event rental, vertical interior agriculture center, a farmer's market, the commercial kitchen, and fresh food market.</t>
   </si>
 </sst>
 </file>
@@ -10516,21 +10509,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61F5F0CF-5ACF-4FDE-9BEB-FAEF4F063264}">
   <dimension ref="A1:G603"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" customWidth="1"/>
-    <col min="7" max="7" width="113.44140625" customWidth="1"/>
-    <col min="8" max="8" width="0.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="113.42578125" customWidth="1"/>
+    <col min="8" max="8" width="0.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -10539,9 +10532,9 @@
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -10550,9 +10543,9 @@
       <c r="F2" s="21"/>
       <c r="G2" s="21"/>
     </row>
-    <row r="3" spans="1:7" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -10561,7 +10554,7 @@
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" spans="1:7" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -10584,7 +10577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
@@ -10607,7 +10600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -10628,9 +10621,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>16</v>
@@ -10649,9 +10642,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>20</v>
@@ -10672,7 +10665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
@@ -10693,7 +10686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
@@ -10711,10 +10704,10 @@
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="2" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -10735,7 +10728,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
@@ -10758,7 +10751,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
@@ -10779,7 +10772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>36</v>
       </c>
@@ -10800,7 +10793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
@@ -10821,7 +10814,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
@@ -10844,7 +10837,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>46</v>
       </c>
@@ -10864,10 +10857,10 @@
         <v>2000000</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>48</v>
       </c>
@@ -10890,7 +10883,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>51</v>
       </c>
@@ -10910,10 +10903,10 @@
         <v>250000</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
@@ -10934,7 +10927,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>57</v>
       </c>
@@ -10955,7 +10948,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>61</v>
       </c>
@@ -10976,7 +10969,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>64</v>
       </c>
@@ -10996,10 +10989,10 @@
         <v>1000000</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>67</v>
       </c>
@@ -11022,7 +11015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>70</v>
       </c>
@@ -11042,10 +11035,10 @@
         <v>1000000</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>72</v>
       </c>
@@ -11063,10 +11056,10 @@
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="2" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>75</v>
       </c>
@@ -11089,7 +11082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>78</v>
       </c>
@@ -11107,10 +11100,10 @@
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="2" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>81</v>
       </c>
@@ -11131,7 +11124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>85</v>
       </c>
@@ -11154,7 +11147,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>88</v>
       </c>
@@ -11174,10 +11167,10 @@
         <v>1250000</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>91</v>
       </c>
@@ -11200,7 +11193,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>95</v>
       </c>
@@ -11220,10 +11213,10 @@
         <v>2000000</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>97</v>
       </c>
@@ -11244,7 +11237,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>100</v>
       </c>
@@ -11267,7 +11260,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>103</v>
       </c>
@@ -11290,7 +11283,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>107</v>
       </c>
@@ -11310,10 +11303,10 @@
         <v>750000</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>109</v>
       </c>
@@ -11333,10 +11326,10 @@
         <v>500000</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>110</v>
       </c>
@@ -11357,7 +11350,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>113</v>
       </c>
@@ -11380,7 +11373,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>116</v>
       </c>
@@ -11403,7 +11396,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>119</v>
       </c>
@@ -11423,10 +11416,10 @@
         <v>1000000</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>121</v>
       </c>
@@ -11446,10 +11439,10 @@
         <v>6000000</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>123</v>
       </c>
@@ -11469,10 +11462,10 @@
         <v>1000000</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>124</v>
       </c>
@@ -11492,10 +11485,10 @@
         <v>1000000</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>127</v>
       </c>
@@ -11513,10 +11506,10 @@
       </c>
       <c r="F46" s="19"/>
       <c r="G46" s="2" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>129</v>
       </c>
@@ -11539,7 +11532,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>133</v>
       </c>
@@ -11560,7 +11553,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>136</v>
       </c>
@@ -11578,10 +11571,10 @@
       </c>
       <c r="F49" s="19"/>
       <c r="G49" s="2" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>138</v>
       </c>
@@ -11601,10 +11594,10 @@
         <v>3500000</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>140</v>
       </c>
@@ -11625,7 +11618,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>143</v>
       </c>
@@ -11648,7 +11641,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>146</v>
       </c>
@@ -11671,7 +11664,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>148</v>
       </c>
@@ -11691,10 +11684,10 @@
         <v>1100000</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>150</v>
       </c>
@@ -11712,10 +11705,10 @@
       </c>
       <c r="F55" s="19"/>
       <c r="G55" s="2" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>152</v>
       </c>
@@ -11735,10 +11728,10 @@
         <v>500000</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>153</v>
       </c>
@@ -11758,10 +11751,10 @@
         <v>500000</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>155</v>
       </c>
@@ -11781,10 +11774,10 @@
         <v>1000000</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>157</v>
       </c>
@@ -11807,7 +11800,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>160</v>
       </c>
@@ -11825,10 +11818,10 @@
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="2" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>163</v>
       </c>
@@ -11848,10 +11841,10 @@
         <v>3000000</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>164</v>
       </c>
@@ -11871,10 +11864,10 @@
         <v>4000000</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>166</v>
       </c>
@@ -11894,10 +11887,10 @@
         <v>1000000</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>169</v>
       </c>
@@ -11920,7 +11913,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>172</v>
       </c>
@@ -11938,10 +11931,10 @@
       </c>
       <c r="F65" s="19"/>
       <c r="G65" s="2" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>175</v>
       </c>
@@ -11961,10 +11954,10 @@
         <v>1000000</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>176</v>
       </c>
@@ -11985,7 +11978,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>179</v>
       </c>
@@ -12008,7 +12001,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>183</v>
       </c>
@@ -12028,10 +12021,10 @@
         <v>750000</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>185</v>
       </c>
@@ -12054,7 +12047,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>188</v>
       </c>
@@ -12077,7 +12070,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>192</v>
       </c>
@@ -12100,7 +12093,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>196</v>
       </c>
@@ -12123,7 +12116,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>199</v>
       </c>
@@ -12141,10 +12134,10 @@
       </c>
       <c r="F74" s="19"/>
       <c r="G74" s="2" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>201</v>
       </c>
@@ -12162,10 +12155,10 @@
       </c>
       <c r="F75" s="19"/>
       <c r="G75" s="2" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>203</v>
       </c>
@@ -12186,7 +12179,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>205</v>
       </c>
@@ -12209,7 +12202,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>208</v>
       </c>
@@ -12229,10 +12222,10 @@
         <v>1500000</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>211</v>
       </c>
@@ -12250,15 +12243,15 @@
       </c>
       <c r="F79" s="19"/>
       <c r="G79" s="2" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>213</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>17</v>
@@ -12276,7 +12269,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>215</v>
       </c>
@@ -12294,10 +12287,10 @@
       </c>
       <c r="F81" s="19"/>
       <c r="G81" s="2" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>217</v>
       </c>
@@ -12320,7 +12313,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>221</v>
       </c>
@@ -12338,10 +12331,10 @@
       </c>
       <c r="F83" s="19"/>
       <c r="G83" s="2" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>223</v>
       </c>
@@ -12362,7 +12355,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>226</v>
       </c>
@@ -12380,10 +12373,10 @@
       </c>
       <c r="F85" s="19"/>
       <c r="G85" s="2" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>228</v>
       </c>
@@ -12404,7 +12397,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>232</v>
       </c>
@@ -12424,10 +12417,10 @@
         <v>250000</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>235</v>
       </c>
@@ -12450,7 +12443,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>239</v>
       </c>
@@ -12468,10 +12461,10 @@
       </c>
       <c r="F89" s="19"/>
       <c r="G89" s="2" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>241</v>
       </c>
@@ -12491,10 +12484,10 @@
         <v>8000000</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>244</v>
       </c>
@@ -12514,10 +12507,10 @@
         <v>500000</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>246</v>
       </c>
@@ -12537,10 +12530,10 @@
         <v>1000000</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>248</v>
       </c>
@@ -12563,7 +12556,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>250</v>
       </c>
@@ -12581,10 +12574,10 @@
       </c>
       <c r="F94" s="19"/>
       <c r="G94" s="2" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>252</v>
       </c>
@@ -12605,7 +12598,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>256</v>
       </c>
@@ -12623,10 +12616,10 @@
       </c>
       <c r="F96" s="19"/>
       <c r="G96" s="2" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>258</v>
       </c>
@@ -12649,7 +12642,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>260</v>
       </c>
@@ -12669,10 +12662,10 @@
         <v>1000000</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>263</v>
       </c>
@@ -12692,10 +12685,10 @@
         <v>500000</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>267</v>
       </c>
@@ -12718,7 +12711,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>271</v>
       </c>
@@ -12738,10 +12731,10 @@
         <v>1000000</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>274</v>
       </c>
@@ -12762,7 +12755,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>279</v>
       </c>
@@ -12785,7 +12778,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>283</v>
       </c>
@@ -12808,7 +12801,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>285</v>
       </c>
@@ -12831,7 +12824,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>289</v>
       </c>
@@ -12851,10 +12844,10 @@
         <v>1000000</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>292</v>
       </c>
@@ -12872,10 +12865,10 @@
       </c>
       <c r="F107" s="19"/>
       <c r="G107" s="2" t="s">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>295</v>
       </c>
@@ -12898,7 +12891,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>299</v>
       </c>
@@ -12919,7 +12912,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>304</v>
       </c>
@@ -12939,10 +12932,10 @@
         <v>4000000</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>306</v>
       </c>
@@ -12963,7 +12956,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>309</v>
       </c>
@@ -12981,10 +12974,10 @@
       </c>
       <c r="F112" s="19"/>
       <c r="G112" s="2" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>310</v>
       </c>
@@ -13005,7 +12998,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>313</v>
       </c>
@@ -13025,10 +13018,10 @@
         <v>1000000</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>315</v>
       </c>
@@ -13048,10 +13041,10 @@
         <v>1000000</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>318</v>
       </c>
@@ -13072,7 +13065,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>321</v>
       </c>
@@ -13093,7 +13086,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>325</v>
       </c>
@@ -13114,7 +13107,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>327</v>
       </c>
@@ -13135,7 +13128,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>331</v>
       </c>
@@ -13158,7 +13151,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>336</v>
       </c>
@@ -13176,10 +13169,10 @@
       </c>
       <c r="F121" s="19"/>
       <c r="G121" s="2" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>339</v>
       </c>
@@ -13202,7 +13195,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>343</v>
       </c>
@@ -13223,7 +13216,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>347</v>
       </c>
@@ -13244,7 +13237,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>352</v>
       </c>
@@ -13267,7 +13260,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>357</v>
       </c>
@@ -13290,7 +13283,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>360</v>
       </c>
@@ -13313,7 +13306,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>363</v>
       </c>
@@ -13334,7 +13327,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>367</v>
       </c>
@@ -13355,7 +13348,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>370</v>
       </c>
@@ -13378,7 +13371,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>374</v>
       </c>
@@ -13399,7 +13392,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>378</v>
       </c>
@@ -13420,7 +13413,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>382</v>
       </c>
@@ -13441,7 +13434,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>385</v>
       </c>
@@ -13459,10 +13452,10 @@
       </c>
       <c r="F134" s="19"/>
       <c r="G134" s="2" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>387</v>
       </c>
@@ -13482,10 +13475,10 @@
         <v>1000000</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>390</v>
       </c>
@@ -13506,7 +13499,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>393</v>
       </c>
@@ -13529,7 +13522,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>396</v>
       </c>
@@ -13549,10 +13542,10 @@
         <v>500000</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>398</v>
       </c>
@@ -13575,7 +13568,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>400</v>
       </c>
@@ -13593,10 +13586,10 @@
       </c>
       <c r="F140" s="19"/>
       <c r="G140" s="2" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>401</v>
       </c>
@@ -13619,7 +13612,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>404</v>
       </c>
@@ -13640,7 +13633,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>408</v>
       </c>
@@ -13660,10 +13653,10 @@
         <v>750000</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>412</v>
       </c>
@@ -13684,7 +13677,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>416</v>
       </c>
@@ -13705,7 +13698,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>420</v>
       </c>
@@ -13725,10 +13718,10 @@
         <v>1000000</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>423</v>
       </c>
@@ -13749,7 +13742,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>428</v>
       </c>
@@ -13767,10 +13760,10 @@
       </c>
       <c r="F148" s="19"/>
       <c r="G148" s="2" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>431</v>
       </c>
@@ -13788,10 +13781,10 @@
       </c>
       <c r="F149" s="19"/>
       <c r="G149" s="2" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>434</v>
       </c>
@@ -13809,10 +13802,10 @@
       </c>
       <c r="F150" s="19"/>
       <c r="G150" s="2" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>435</v>
       </c>
@@ -13832,10 +13825,10 @@
         <v>1400000</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>438</v>
       </c>
@@ -13858,7 +13851,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>441</v>
       </c>
@@ -13881,7 +13874,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>445</v>
       </c>
@@ -13899,10 +13892,10 @@
       </c>
       <c r="F154" s="19"/>
       <c r="G154" s="2" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>449</v>
       </c>
@@ -13925,7 +13918,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>453</v>
       </c>
@@ -13945,10 +13938,10 @@
         <v>2000000</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>456</v>
       </c>
@@ -13969,7 +13962,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>461</v>
       </c>
@@ -13992,7 +13985,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>466</v>
       </c>
@@ -14015,7 +14008,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>469</v>
       </c>
@@ -14038,7 +14031,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>473</v>
       </c>
@@ -14059,7 +14052,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>478</v>
       </c>
@@ -14080,7 +14073,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>481</v>
       </c>
@@ -14103,7 +14096,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>485</v>
       </c>
@@ -14124,7 +14117,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>489</v>
       </c>
@@ -14147,7 +14140,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>493</v>
       </c>
@@ -14170,7 +14163,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>497</v>
       </c>
@@ -14191,7 +14184,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>501</v>
       </c>
@@ -14212,7 +14205,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>505</v>
       </c>
@@ -14233,7 +14226,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>508</v>
       </c>
@@ -14256,7 +14249,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>512</v>
       </c>
@@ -14277,7 +14270,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>516</v>
       </c>
@@ -14300,7 +14293,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>520</v>
       </c>
@@ -14323,7 +14316,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>523</v>
       </c>
@@ -14346,7 +14339,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>527</v>
       </c>
@@ -14369,7 +14362,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>530</v>
       </c>
@@ -14392,7 +14385,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>535</v>
       </c>
@@ -14415,7 +14408,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>540</v>
       </c>
@@ -14438,7 +14431,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>544</v>
       </c>
@@ -14461,7 +14454,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>547</v>
       </c>
@@ -14484,7 +14477,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>552</v>
       </c>
@@ -14507,7 +14500,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>557</v>
       </c>
@@ -14528,7 +14521,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>561</v>
       </c>
@@ -14551,7 +14544,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>566</v>
       </c>
@@ -14574,7 +14567,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>570</v>
       </c>
@@ -14597,7 +14590,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>574</v>
       </c>
@@ -14620,7 +14613,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>578</v>
       </c>
@@ -14641,7 +14634,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>583</v>
       </c>
@@ -14662,7 +14655,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>586</v>
       </c>
@@ -14683,7 +14676,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>589</v>
       </c>
@@ -14704,7 +14697,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>593</v>
       </c>
@@ -14725,7 +14718,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>596</v>
       </c>
@@ -14746,7 +14739,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>599</v>
       </c>
@@ -14767,7 +14760,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>602</v>
       </c>
@@ -14790,7 +14783,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>606</v>
       </c>
@@ -14813,7 +14806,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>609</v>
       </c>
@@ -14836,7 +14829,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>612</v>
       </c>
@@ -14857,7 +14850,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>615</v>
       </c>
@@ -14880,7 +14873,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>619</v>
       </c>
@@ -14901,7 +14894,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>623</v>
       </c>
@@ -14922,7 +14915,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>626</v>
       </c>
@@ -14945,7 +14938,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>629</v>
       </c>
@@ -14966,7 +14959,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
         <v>634</v>
       </c>
@@ -14987,7 +14980,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>637</v>
       </c>
@@ -15008,7 +15001,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>640</v>
       </c>
@@ -15029,7 +15022,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>644</v>
       </c>
@@ -15050,7 +15043,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
         <v>647</v>
       </c>
@@ -15073,7 +15066,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>651</v>
       </c>
@@ -15094,7 +15087,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
         <v>654</v>
       </c>
@@ -15117,7 +15110,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>658</v>
       </c>
@@ -15140,7 +15133,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
         <v>662</v>
       </c>
@@ -15163,7 +15156,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>665</v>
       </c>
@@ -15186,7 +15179,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
         <v>669</v>
       </c>
@@ -15207,7 +15200,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>672</v>
       </c>
@@ -15228,7 +15221,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
         <v>675</v>
       </c>
@@ -15251,7 +15244,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>678</v>
       </c>
@@ -15272,7 +15265,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
         <v>681</v>
       </c>
@@ -15295,7 +15288,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>684</v>
       </c>
@@ -15318,7 +15311,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
         <v>687</v>
       </c>
@@ -15341,7 +15334,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>691</v>
       </c>
@@ -15362,7 +15355,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
         <v>694</v>
       </c>
@@ -15383,7 +15376,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>697</v>
       </c>
@@ -15406,7 +15399,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
         <v>701</v>
       </c>
@@ -15429,7 +15422,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>704</v>
       </c>
@@ -15452,7 +15445,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
         <v>707</v>
       </c>
@@ -15473,7 +15466,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>709</v>
       </c>
@@ -15494,7 +15487,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
         <v>711</v>
       </c>
@@ -15517,7 +15510,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>715</v>
       </c>
@@ -15538,7 +15531,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
         <v>719</v>
       </c>
@@ -15561,7 +15554,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>721</v>
       </c>
@@ -15584,7 +15577,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
         <v>724</v>
       </c>
@@ -15607,7 +15600,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
         <v>729</v>
       </c>
@@ -15630,7 +15623,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
         <v>734</v>
       </c>
@@ -15653,7 +15646,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>737</v>
       </c>
@@ -15676,7 +15669,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
         <v>740</v>
       </c>
@@ -15699,7 +15692,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>743</v>
       </c>
@@ -15722,7 +15715,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
         <v>746</v>
       </c>
@@ -15743,7 +15736,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
         <v>749</v>
       </c>
@@ -15764,7 +15757,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
         <v>753</v>
       </c>
@@ -15785,7 +15778,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
         <v>756</v>
       </c>
@@ -15808,7 +15801,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
         <v>759</v>
       </c>
@@ -15831,7 +15824,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
         <v>762</v>
       </c>
@@ -15854,7 +15847,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
         <v>765</v>
       </c>
@@ -15875,7 +15868,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A244" s="13" t="s">
         <v>768</v>
       </c>
@@ -15898,9 +15891,9 @@
         <v>769</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>730</v>
@@ -15918,10 +15911,10 @@
         <v>3000000</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>770</v>
       </c>
@@ -15942,7 +15935,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
         <v>773</v>
       </c>
@@ -15965,7 +15958,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
         <v>778</v>
       </c>
@@ -15986,7 +15979,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
         <v>782</v>
       </c>
@@ -16009,7 +16002,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
         <v>786</v>
       </c>
@@ -16030,7 +16023,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
         <v>790</v>
       </c>
@@ -16053,7 +16046,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
         <v>794</v>
       </c>
@@ -16076,7 +16069,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
         <v>799</v>
       </c>
@@ -16097,7 +16090,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
         <v>803</v>
       </c>
@@ -16118,7 +16111,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
         <v>807</v>
       </c>
@@ -16139,7 +16132,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>810</v>
       </c>
@@ -16162,7 +16155,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
         <v>815</v>
       </c>
@@ -16183,7 +16176,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
         <v>819</v>
       </c>
@@ -16206,7 +16199,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
         <v>822</v>
       </c>
@@ -16227,7 +16220,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>827</v>
       </c>
@@ -16248,7 +16241,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
         <v>831</v>
       </c>
@@ -16269,7 +16262,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
         <v>836</v>
       </c>
@@ -16292,7 +16285,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
         <v>839</v>
       </c>
@@ -16313,12 +16306,12 @@
         <v>842</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
         <v>843</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>833</v>
@@ -16336,7 +16329,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
         <v>846</v>
       </c>
@@ -16357,7 +16350,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>850</v>
       </c>
@@ -16378,7 +16371,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
         <v>853</v>
       </c>
@@ -16399,7 +16392,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
         <v>857</v>
       </c>
@@ -16420,7 +16413,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>860</v>
       </c>
@@ -16441,7 +16434,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>864</v>
       </c>
@@ -16462,7 +16455,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>867</v>
       </c>
@@ -16485,7 +16478,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>870</v>
       </c>
@@ -16506,7 +16499,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>872</v>
       </c>
@@ -16529,7 +16522,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>875</v>
       </c>
@@ -16550,7 +16543,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>879</v>
       </c>
@@ -16571,7 +16564,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>882</v>
       </c>
@@ -16592,7 +16585,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>885</v>
       </c>
@@ -16613,7 +16606,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
         <v>888</v>
       </c>
@@ -16634,7 +16627,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
         <v>891</v>
       </c>
@@ -16655,7 +16648,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
         <v>894</v>
       </c>
@@ -16676,7 +16669,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
         <v>897</v>
       </c>
@@ -16697,7 +16690,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
         <v>900</v>
       </c>
@@ -16718,7 +16711,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
         <v>903</v>
       </c>
@@ -16741,7 +16734,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
         <v>906</v>
       </c>
@@ -16764,7 +16757,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A285" s="6" t="s">
         <v>909</v>
       </c>
@@ -16785,7 +16778,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
         <v>912</v>
       </c>
@@ -16806,7 +16799,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
         <v>915</v>
       </c>
@@ -16827,7 +16820,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
         <v>918</v>
       </c>
@@ -16850,7 +16843,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
         <v>921</v>
       </c>
@@ -16871,7 +16864,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
         <v>924</v>
       </c>
@@ -16894,7 +16887,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
         <v>929</v>
       </c>
@@ -16915,7 +16908,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
         <v>932</v>
       </c>
@@ -16938,7 +16931,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
         <v>936</v>
       </c>
@@ -16961,7 +16954,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
         <v>940</v>
       </c>
@@ -16982,7 +16975,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
         <v>944</v>
       </c>
@@ -17005,7 +16998,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
         <v>947</v>
       </c>
@@ -17028,7 +17021,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
         <v>951</v>
       </c>
@@ -17051,7 +17044,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
         <v>955</v>
       </c>
@@ -17074,7 +17067,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
         <v>959</v>
       </c>
@@ -17095,7 +17088,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
         <v>962</v>
       </c>
@@ -17118,7 +17111,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
         <v>965</v>
       </c>
@@ -17141,7 +17134,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
         <v>968</v>
       </c>
@@ -17164,7 +17157,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A303" s="6" t="s">
         <v>971</v>
       </c>
@@ -17187,7 +17180,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
         <v>976</v>
       </c>
@@ -17208,7 +17201,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
         <v>981</v>
       </c>
@@ -17231,7 +17224,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
         <v>985</v>
       </c>
@@ -17254,7 +17247,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
         <v>990</v>
       </c>
@@ -17277,7 +17270,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
         <v>994</v>
       </c>
@@ -17300,7 +17293,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
         <v>997</v>
       </c>
@@ -17323,7 +17316,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A310" s="6" t="s">
         <v>1001</v>
       </c>
@@ -17344,7 +17337,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A311" s="6" t="s">
         <v>1004</v>
       </c>
@@ -17365,7 +17358,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
         <v>1008</v>
       </c>
@@ -17388,7 +17381,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A313" s="6" t="s">
         <v>1011</v>
       </c>
@@ -17411,7 +17404,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
         <v>1014</v>
       </c>
@@ -17434,7 +17427,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A315" s="6" t="s">
         <v>1017</v>
       </c>
@@ -17457,7 +17450,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
         <v>1021</v>
       </c>
@@ -17480,7 +17473,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A317" s="6" t="s">
         <v>1025</v>
       </c>
@@ -17503,7 +17496,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
         <v>1028</v>
       </c>
@@ -17524,7 +17517,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
         <v>1031</v>
       </c>
@@ -17545,7 +17538,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
         <v>1034</v>
       </c>
@@ -17568,7 +17561,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
         <v>1039</v>
       </c>
@@ -17591,7 +17584,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
         <v>1043</v>
       </c>
@@ -17614,7 +17607,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A323" s="6" t="s">
         <v>1047</v>
       </c>
@@ -17635,7 +17628,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
         <v>1051</v>
       </c>
@@ -17658,7 +17651,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A325" s="6" t="s">
         <v>1054</v>
       </c>
@@ -17679,7 +17672,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
         <v>1057</v>
       </c>
@@ -17700,7 +17693,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A327" s="6" t="s">
         <v>1061</v>
       </c>
@@ -17721,7 +17714,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A328" s="6" t="s">
         <v>1065</v>
       </c>
@@ -17744,7 +17737,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A329" s="6" t="s">
         <v>1068</v>
       </c>
@@ -17767,7 +17760,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A330" s="6" t="s">
         <v>1071</v>
       </c>
@@ -17790,7 +17783,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A331" s="6" t="s">
         <v>1074</v>
       </c>
@@ -17811,7 +17804,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A332" s="6" t="s">
         <v>1078</v>
       </c>
@@ -17832,7 +17825,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A333" s="6" t="s">
         <v>1082</v>
       </c>
@@ -17855,7 +17848,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A334" s="6" t="s">
         <v>1086</v>
       </c>
@@ -17876,7 +17869,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A335" s="6" t="s">
         <v>1089</v>
       </c>
@@ -17899,7 +17892,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
         <v>1093</v>
       </c>
@@ -17922,7 +17915,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A337" s="6" t="s">
         <v>1097</v>
       </c>
@@ -17945,7 +17938,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A338" s="6" t="s">
         <v>1101</v>
       </c>
@@ -17956,7 +17949,7 @@
         <v>1036</v>
       </c>
       <c r="D338" s="18" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="E338" s="11">
         <v>600000</v>
@@ -17966,7 +17959,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A339" s="6" t="s">
         <v>1105</v>
       </c>
@@ -17977,7 +17970,7 @@
         <v>1107</v>
       </c>
       <c r="D339" s="18" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="E339" s="11">
         <v>2000000</v>
@@ -17989,7 +17982,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A340" s="6" t="s">
         <v>1109</v>
       </c>
@@ -18010,7 +18003,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A341" s="6" t="s">
         <v>1113</v>
       </c>
@@ -18033,7 +18026,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A342" s="6" t="s">
         <v>1117</v>
       </c>
@@ -18054,7 +18047,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A343" s="6" t="s">
         <v>1120</v>
       </c>
@@ -18075,7 +18068,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A344" s="6" t="s">
         <v>1124</v>
       </c>
@@ -18098,7 +18091,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A345" s="6" t="s">
         <v>1127</v>
       </c>
@@ -18121,7 +18114,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A346" s="6" t="s">
         <v>1132</v>
       </c>
@@ -18144,7 +18137,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A347" s="6" t="s">
         <v>1136</v>
       </c>
@@ -18167,7 +18160,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A348" s="6" t="s">
         <v>1141</v>
       </c>
@@ -18190,7 +18183,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A349" s="6" t="s">
         <v>1145</v>
       </c>
@@ -18213,7 +18206,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A350" s="6" t="s">
         <v>1149</v>
       </c>
@@ -18236,7 +18229,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A351" s="6" t="s">
         <v>1153</v>
       </c>
@@ -18257,7 +18250,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A352" s="6" t="s">
         <v>1157</v>
       </c>
@@ -18280,7 +18273,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A353" s="6" t="s">
         <v>1162</v>
       </c>
@@ -18303,7 +18296,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A354" s="6" t="s">
         <v>1167</v>
       </c>
@@ -18326,7 +18319,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A355" s="6" t="s">
         <v>1171</v>
       </c>
@@ -18349,7 +18342,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A356" s="6" t="s">
         <v>1173</v>
       </c>
@@ -18370,7 +18363,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A357" s="6" t="s">
         <v>1177</v>
       </c>
@@ -18393,7 +18386,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
         <v>1180</v>
       </c>
@@ -18416,7 +18409,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A359" s="6" t="s">
         <v>1183</v>
       </c>
@@ -18437,7 +18430,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A360" s="6" t="s">
         <v>1186</v>
       </c>
@@ -18458,7 +18451,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A361" s="6" t="s">
         <v>1190</v>
       </c>
@@ -18479,7 +18472,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A362" s="6" t="s">
         <v>1195</v>
       </c>
@@ -18500,7 +18493,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A363" s="6" t="s">
         <v>1199</v>
       </c>
@@ -18521,7 +18514,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A364" s="6" t="s">
         <v>1203</v>
       </c>
@@ -18542,7 +18535,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A365" s="6" t="s">
         <v>1207</v>
       </c>
@@ -18563,7 +18556,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A366" s="6" t="s">
         <v>1211</v>
       </c>
@@ -18584,7 +18577,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A367" s="6" t="s">
         <v>1215</v>
       </c>
@@ -18607,7 +18600,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A368" s="6" t="s">
         <v>1219</v>
       </c>
@@ -18630,7 +18623,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A369" s="6" t="s">
         <v>1223</v>
       </c>
@@ -18653,7 +18646,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A370" s="6" t="s">
         <v>1226</v>
       </c>
@@ -18676,7 +18669,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A371" s="6" t="s">
         <v>1229</v>
       </c>
@@ -18697,7 +18690,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A372" s="6" t="s">
         <v>1233</v>
       </c>
@@ -18718,7 +18711,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A373" s="6" t="s">
         <v>1237</v>
       </c>
@@ -18739,7 +18732,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A374" s="6" t="s">
         <v>1241</v>
       </c>
@@ -18762,7 +18755,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A375" s="6" t="s">
         <v>1245</v>
       </c>
@@ -18783,7 +18776,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A376" s="6" t="s">
         <v>1249</v>
       </c>
@@ -18806,7 +18799,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A377" s="6" t="s">
         <v>1253</v>
       </c>
@@ -18829,7 +18822,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A378" s="6" t="s">
         <v>1256</v>
       </c>
@@ -18852,7 +18845,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A379" s="6" t="s">
         <v>1260</v>
       </c>
@@ -18875,7 +18868,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A380" s="6" t="s">
         <v>1263</v>
       </c>
@@ -18898,7 +18891,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A381" s="6" t="s">
         <v>1266</v>
       </c>
@@ -18921,7 +18914,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A382" s="6" t="s">
         <v>1270</v>
       </c>
@@ -18944,7 +18937,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A383" s="6" t="s">
         <v>1274</v>
       </c>
@@ -18967,7 +18960,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A384" s="6" t="s">
         <v>1277</v>
       </c>
@@ -18990,7 +18983,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A385" s="6" t="s">
         <v>1280</v>
       </c>
@@ -19011,7 +19004,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A386" s="6" t="s">
         <v>1283</v>
       </c>
@@ -19034,7 +19027,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A387" s="6" t="s">
         <v>1286</v>
       </c>
@@ -19055,7 +19048,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A388" s="6" t="s">
         <v>1288</v>
       </c>
@@ -19078,7 +19071,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A389" s="6" t="s">
         <v>1291</v>
       </c>
@@ -19101,7 +19094,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A390" s="6" t="s">
         <v>1295</v>
       </c>
@@ -19124,7 +19117,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A391" s="6" t="s">
         <v>1297</v>
       </c>
@@ -19145,7 +19138,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A392" s="6" t="s">
         <v>1299</v>
       </c>
@@ -19166,7 +19159,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A393" s="6" t="s">
         <v>1302</v>
       </c>
@@ -19189,7 +19182,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A394" s="6" t="s">
         <v>1305</v>
       </c>
@@ -19212,7 +19205,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A395" s="6" t="s">
         <v>1308</v>
       </c>
@@ -19235,7 +19228,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A396" s="6" t="s">
         <v>1313</v>
       </c>
@@ -19258,7 +19251,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A397" s="6" t="s">
         <v>1317</v>
       </c>
@@ -19281,7 +19274,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A398" s="6" t="s">
         <v>1320</v>
       </c>
@@ -19304,7 +19297,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A399" s="6" t="s">
         <v>1323</v>
       </c>
@@ -19325,7 +19318,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A400" s="6" t="s">
         <v>1326</v>
       </c>
@@ -19346,7 +19339,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A401" s="6" t="s">
         <v>1329</v>
       </c>
@@ -19369,7 +19362,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A402" s="6" t="s">
         <v>1332</v>
       </c>
@@ -19392,7 +19385,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A403" s="6" t="s">
         <v>1336</v>
       </c>
@@ -19413,7 +19406,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A404" s="6" t="s">
         <v>1339</v>
       </c>
@@ -19421,7 +19414,7 @@
         <v>1340</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>1342</v>
@@ -19436,7 +19429,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A405" s="6" t="s">
         <v>1344</v>
       </c>
@@ -19459,7 +19452,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A406" s="6" t="s">
         <v>1348</v>
       </c>
@@ -19482,7 +19475,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A407" s="6" t="s">
         <v>1351</v>
       </c>
@@ -19505,7 +19498,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A408" s="6" t="s">
         <v>1355</v>
       </c>
@@ -19528,7 +19521,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A409" s="6" t="s">
         <v>1360</v>
       </c>
@@ -19549,7 +19542,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A410" s="6" t="s">
         <v>1363</v>
       </c>
@@ -19572,7 +19565,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A411" s="6" t="s">
         <v>1368</v>
       </c>
@@ -19593,7 +19586,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A412" s="6" t="s">
         <v>1371</v>
       </c>
@@ -19614,7 +19607,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A413" s="6" t="s">
         <v>1374</v>
       </c>
@@ -19637,7 +19630,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A414" s="6" t="s">
         <v>1377</v>
       </c>
@@ -19660,7 +19653,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A415" s="6" t="s">
         <v>1380</v>
       </c>
@@ -19683,7 +19676,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A416" s="6" t="s">
         <v>1383</v>
       </c>
@@ -19704,7 +19697,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
         <v>1386</v>
       </c>
@@ -19727,7 +19720,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A418" s="6" t="s">
         <v>1389</v>
       </c>
@@ -19748,7 +19741,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A419" s="6" t="s">
         <v>1392</v>
       </c>
@@ -19771,7 +19764,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A420" s="6" t="s">
         <v>1395</v>
       </c>
@@ -19794,7 +19787,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A421" s="6" t="s">
         <v>1398</v>
       </c>
@@ -19815,7 +19808,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A422" s="6" t="s">
         <v>1401</v>
       </c>
@@ -19836,7 +19829,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A423" s="6" t="s">
         <v>1403</v>
       </c>
@@ -19857,7 +19850,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A424" s="6" t="s">
         <v>1406</v>
       </c>
@@ -19880,7 +19873,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A425" s="6" t="s">
         <v>1409</v>
       </c>
@@ -19901,7 +19894,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A426" s="6" t="s">
         <v>1412</v>
       </c>
@@ -19922,7 +19915,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A427" s="6" t="s">
         <v>1415</v>
       </c>
@@ -19945,7 +19938,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A428" s="6" t="s">
         <v>1418</v>
       </c>
@@ -19966,7 +19959,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A429" s="6" t="s">
         <v>1421</v>
       </c>
@@ -19989,7 +19982,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A430" s="6" t="s">
         <v>1424</v>
       </c>
@@ -20012,7 +20005,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A431" s="6" t="s">
         <v>1427</v>
       </c>
@@ -20035,7 +20028,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A432" s="6" t="s">
         <v>1430</v>
       </c>
@@ -20058,7 +20051,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A433" s="6" t="s">
         <v>1433</v>
       </c>
@@ -20081,7 +20074,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A434" s="6" t="s">
         <v>1436</v>
       </c>
@@ -20102,7 +20095,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A435" s="6" t="s">
         <v>1439</v>
       </c>
@@ -20125,7 +20118,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A436" s="6" t="s">
         <v>1441</v>
       </c>
@@ -20148,7 +20141,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A437" s="6" t="s">
         <v>1444</v>
       </c>
@@ -20171,7 +20164,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A438" s="6" t="s">
         <v>1447</v>
       </c>
@@ -20192,7 +20185,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A439" s="6" t="s">
         <v>1450</v>
       </c>
@@ -20215,7 +20208,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A440" s="6" t="s">
         <v>1453</v>
       </c>
@@ -20236,7 +20229,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A441" s="6" t="s">
         <v>1456</v>
       </c>
@@ -20257,7 +20250,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A442" s="6" t="s">
         <v>1459</v>
       </c>
@@ -20280,7 +20273,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A443" s="6" t="s">
         <v>1462</v>
       </c>
@@ -20303,7 +20296,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A444" s="6" t="s">
         <v>1465</v>
       </c>
@@ -20326,7 +20319,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A445" s="6" t="s">
         <v>1468</v>
       </c>
@@ -20349,7 +20342,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A446" s="6" t="s">
         <v>1471</v>
       </c>
@@ -20372,7 +20365,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A447" s="6" t="s">
         <v>1474</v>
       </c>
@@ -20395,7 +20388,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A448" s="6" t="s">
         <v>1477</v>
       </c>
@@ -20418,7 +20411,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A449" s="6" t="s">
         <v>1480</v>
       </c>
@@ -20439,7 +20432,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A450" s="6" t="s">
         <v>1483</v>
       </c>
@@ -20460,7 +20453,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A451" s="6" t="s">
         <v>1486</v>
       </c>
@@ -20481,7 +20474,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A452" s="6" t="s">
         <v>1489</v>
       </c>
@@ -20502,7 +20495,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A453" s="6" t="s">
         <v>1492</v>
       </c>
@@ -20525,7 +20518,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A454" s="6" t="s">
         <v>1495</v>
       </c>
@@ -20548,7 +20541,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A455" s="6" t="s">
         <v>1497</v>
       </c>
@@ -20571,7 +20564,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A456" s="6" t="s">
         <v>1500</v>
       </c>
@@ -20592,7 +20585,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A457" s="6" t="s">
         <v>1503</v>
       </c>
@@ -20613,7 +20606,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A458" s="6" t="s">
         <v>1506</v>
       </c>
@@ -20636,7 +20629,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A459" s="6" t="s">
         <v>1509</v>
       </c>
@@ -20659,7 +20652,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A460" s="6" t="s">
         <v>1512</v>
       </c>
@@ -20682,7 +20675,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A461" s="6" t="s">
         <v>1515</v>
       </c>
@@ -20705,7 +20698,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A462" s="6" t="s">
         <v>1518</v>
       </c>
@@ -20728,7 +20721,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A463" s="6" t="s">
         <v>1521</v>
       </c>
@@ -20749,7 +20742,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A464" s="6" t="s">
         <v>1524</v>
       </c>
@@ -20772,7 +20765,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A465" s="6" t="s">
         <v>1527</v>
       </c>
@@ -20793,7 +20786,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A466" s="6" t="s">
         <v>1530</v>
       </c>
@@ -20816,7 +20809,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A467" s="6" t="s">
         <v>1533</v>
       </c>
@@ -20837,7 +20830,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A468" s="6" t="s">
         <v>1536</v>
       </c>
@@ -20860,7 +20853,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A469" s="6" t="s">
         <v>1539</v>
       </c>
@@ -20883,7 +20876,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A470" s="6" t="s">
         <v>1542</v>
       </c>
@@ -20906,7 +20899,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A471" s="6" t="s">
         <v>1545</v>
       </c>
@@ -20929,7 +20922,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A472" s="6" t="s">
         <v>1548</v>
       </c>
@@ -20952,7 +20945,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A473" s="6" t="s">
         <v>1551</v>
       </c>
@@ -20975,7 +20968,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" ht="51" x14ac:dyDescent="0.25">
       <c r="A474" s="6" t="s">
         <v>1554</v>
       </c>
@@ -20996,7 +20989,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A475" s="6" t="s">
         <v>1557</v>
       </c>
@@ -21017,7 +21010,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
         <v>1560</v>
       </c>
@@ -21038,7 +21031,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A477" s="6" t="s">
         <v>1563</v>
       </c>
@@ -21061,7 +21054,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A478" s="6" t="s">
         <v>1566</v>
       </c>
@@ -21082,7 +21075,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A479" s="6" t="s">
         <v>1569</v>
       </c>
@@ -21103,7 +21096,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A480" s="6" t="s">
         <v>1572</v>
       </c>
@@ -21126,7 +21119,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A481" s="6" t="s">
         <v>1575</v>
       </c>
@@ -21149,7 +21142,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A482" s="6" t="s">
         <v>1578</v>
       </c>
@@ -21170,7 +21163,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A483" s="6" t="s">
         <v>1581</v>
       </c>
@@ -21191,7 +21184,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A484" s="6" t="s">
         <v>1584</v>
       </c>
@@ -21214,7 +21207,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A485" s="6" t="s">
         <v>1587</v>
       </c>
@@ -21237,7 +21230,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A486" s="6" t="s">
         <v>1590</v>
       </c>
@@ -21258,7 +21251,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A487" s="6" t="s">
         <v>1593</v>
       </c>
@@ -21278,15 +21271,15 @@
         <v>1000000</v>
       </c>
       <c r="G487" s="2" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A488" s="6" t="s">
         <v>1595</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A488" s="6" t="s">
+      <c r="B488" s="6" t="s">
         <v>1596</v>
-      </c>
-      <c r="B488" s="6" t="s">
-        <v>1597</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>1365</v>
@@ -21301,15 +21294,15 @@
         <v>750000</v>
       </c>
       <c r="G488" s="2" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A489" s="6" t="s">
         <v>1598</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A489" s="6" t="s">
+      <c r="B489" s="6" t="s">
         <v>1599</v>
-      </c>
-      <c r="B489" s="6" t="s">
-        <v>1600</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>1365</v>
@@ -21324,15 +21317,15 @@
         <v>1000000</v>
       </c>
       <c r="G489" s="2" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A490" s="6" t="s">
         <v>1601</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A490" s="6" t="s">
+      <c r="B490" s="6" t="s">
         <v>1602</v>
-      </c>
-      <c r="B490" s="6" t="s">
-        <v>1603</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>1365</v>
@@ -21347,15 +21340,15 @@
         <v>1000000</v>
       </c>
       <c r="G490" s="2" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A491" s="6" t="s">
         <v>1604</v>
       </c>
-    </row>
-    <row r="491" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A491" s="6" t="s">
+      <c r="B491" s="6" t="s">
         <v>1605</v>
-      </c>
-      <c r="B491" s="6" t="s">
-        <v>1606</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>1365</v>
@@ -21368,15 +21361,15 @@
       </c>
       <c r="F491" s="19"/>
       <c r="G491" s="2" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A492" s="6" t="s">
         <v>1607</v>
       </c>
-    </row>
-    <row r="492" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A492" s="6" t="s">
+      <c r="B492" s="6" t="s">
         <v>1608</v>
-      </c>
-      <c r="B492" s="6" t="s">
-        <v>1609</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>1365</v>
@@ -21389,15 +21382,15 @@
       </c>
       <c r="F492" s="19"/>
       <c r="G492" s="2" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A493" s="6" t="s">
         <v>1610</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A493" s="6" t="s">
+      <c r="B493" s="6" t="s">
         <v>1611</v>
-      </c>
-      <c r="B493" s="6" t="s">
-        <v>1612</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>1365</v>
@@ -21412,15 +21405,15 @@
         <v>1500000</v>
       </c>
       <c r="G493" s="2" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A494" s="6" t="s">
         <v>1613</v>
       </c>
-    </row>
-    <row r="494" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A494" s="6" t="s">
+      <c r="B494" s="6" t="s">
         <v>1614</v>
-      </c>
-      <c r="B494" s="6" t="s">
-        <v>1615</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>1365</v>
@@ -21435,15 +21428,15 @@
         <v>500000</v>
       </c>
       <c r="G494" s="2" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A495" s="6" t="s">
         <v>1616</v>
       </c>
-    </row>
-    <row r="495" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A495" s="6" t="s">
+      <c r="B495" s="6" t="s">
         <v>1617</v>
-      </c>
-      <c r="B495" s="6" t="s">
-        <v>1618</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>1365</v>
@@ -21458,15 +21451,15 @@
         <v>4000000</v>
       </c>
       <c r="G495" s="2" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A496" s="6" t="s">
         <v>1619</v>
       </c>
-    </row>
-    <row r="496" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A496" s="6" t="s">
+      <c r="B496" s="6" t="s">
         <v>1620</v>
-      </c>
-      <c r="B496" s="6" t="s">
-        <v>1621</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>1365</v>
@@ -21479,15 +21472,15 @@
       </c>
       <c r="F496" s="19"/>
       <c r="G496" s="2" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A497" s="6" t="s">
         <v>1622</v>
       </c>
-    </row>
-    <row r="497" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A497" s="6" t="s">
+      <c r="B497" s="6" t="s">
         <v>1623</v>
-      </c>
-      <c r="B497" s="6" t="s">
-        <v>1624</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>1365</v>
@@ -21502,15 +21495,15 @@
         <v>1500000</v>
       </c>
       <c r="G497" s="2" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A498" s="6" t="s">
         <v>1625</v>
       </c>
-    </row>
-    <row r="498" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A498" s="6" t="s">
+      <c r="B498" s="6" t="s">
         <v>1626</v>
-      </c>
-      <c r="B498" s="6" t="s">
-        <v>1627</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>1365</v>
@@ -21525,15 +21518,15 @@
         <v>500000</v>
       </c>
       <c r="G498" s="2" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A499" s="6" t="s">
         <v>1628</v>
       </c>
-    </row>
-    <row r="499" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A499" s="6" t="s">
+      <c r="B499" s="6" t="s">
         <v>1629</v>
-      </c>
-      <c r="B499" s="6" t="s">
-        <v>1630</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>1365</v>
@@ -21548,15 +21541,15 @@
         <v>2000000</v>
       </c>
       <c r="G499" s="2" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A500" s="6" t="s">
         <v>1631</v>
       </c>
-    </row>
-    <row r="500" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A500" s="6" t="s">
+      <c r="B500" s="6" t="s">
         <v>1632</v>
-      </c>
-      <c r="B500" s="6" t="s">
-        <v>1633</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>1365</v>
@@ -21569,15 +21562,15 @@
       </c>
       <c r="F500" s="19"/>
       <c r="G500" s="2" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A501" s="6" t="s">
         <v>1634</v>
       </c>
-    </row>
-    <row r="501" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A501" s="6" t="s">
+      <c r="B501" s="6" t="s">
         <v>1635</v>
-      </c>
-      <c r="B501" s="6" t="s">
-        <v>1636</v>
       </c>
       <c r="C501" s="1" t="s">
         <v>1365</v>
@@ -21592,15 +21585,15 @@
         <v>1000000</v>
       </c>
       <c r="G501" s="2" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A502" s="6" t="s">
         <v>1637</v>
       </c>
-    </row>
-    <row r="502" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A502" s="6" t="s">
+      <c r="B502" s="6" t="s">
         <v>1638</v>
-      </c>
-      <c r="B502" s="6" t="s">
-        <v>1639</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>1365</v>
@@ -21615,15 +21608,15 @@
         <v>500000</v>
       </c>
       <c r="G502" s="2" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A503" s="6" t="s">
         <v>1640</v>
       </c>
-    </row>
-    <row r="503" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A503" s="6" t="s">
+      <c r="B503" s="6" t="s">
         <v>1641</v>
-      </c>
-      <c r="B503" s="6" t="s">
-        <v>1642</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>1365</v>
@@ -21636,15 +21629,15 @@
       </c>
       <c r="F503" s="19"/>
       <c r="G503" s="2" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A504" s="6" t="s">
         <v>1643</v>
       </c>
-    </row>
-    <row r="504" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A504" s="6" t="s">
+      <c r="B504" s="6" t="s">
         <v>1644</v>
-      </c>
-      <c r="B504" s="6" t="s">
-        <v>1645</v>
       </c>
       <c r="C504" s="1" t="s">
         <v>1365</v>
@@ -21659,12 +21652,12 @@
         <v>2000000</v>
       </c>
       <c r="G504" s="2" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A505" s="6" t="s">
         <v>1646</v>
-      </c>
-    </row>
-    <row r="505" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A505" s="6" t="s">
-        <v>1647</v>
       </c>
       <c r="B505" s="6" t="s">
         <v>405</v>
@@ -21683,12 +21676,12 @@
         <v>407</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A506" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B506" s="6" t="s">
         <v>1648</v>
-      </c>
-      <c r="B506" s="6" t="s">
-        <v>1649</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>1365</v>
@@ -21703,15 +21696,15 @@
         <v>2000000</v>
       </c>
       <c r="G506" s="2" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A507" s="6" t="s">
         <v>1650</v>
       </c>
-    </row>
-    <row r="507" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A507" s="6" t="s">
+      <c r="B507" s="6" t="s">
         <v>1651</v>
-      </c>
-      <c r="B507" s="6" t="s">
-        <v>1652</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>1365</v>
@@ -21726,15 +21719,15 @@
         <v>500000</v>
       </c>
       <c r="G507" s="2" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A508" s="6" t="s">
         <v>1653</v>
       </c>
-    </row>
-    <row r="508" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A508" s="6" t="s">
+      <c r="B508" s="6" t="s">
         <v>1654</v>
-      </c>
-      <c r="B508" s="6" t="s">
-        <v>1655</v>
       </c>
       <c r="C508" s="1" t="s">
         <v>1365</v>
@@ -21749,15 +21742,15 @@
         <v>1000000</v>
       </c>
       <c r="G508" s="2" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A509" s="6" t="s">
         <v>1656</v>
       </c>
-    </row>
-    <row r="509" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A509" s="6" t="s">
+      <c r="B509" s="6" t="s">
         <v>1657</v>
-      </c>
-      <c r="B509" s="6" t="s">
-        <v>1658</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>1365</v>
@@ -21772,15 +21765,15 @@
         <v>500000</v>
       </c>
       <c r="G509" s="2" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A510" s="6" t="s">
         <v>1659</v>
       </c>
-    </row>
-    <row r="510" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A510" s="6" t="s">
+      <c r="B510" s="6" t="s">
         <v>1660</v>
-      </c>
-      <c r="B510" s="6" t="s">
-        <v>1661</v>
       </c>
       <c r="C510" s="1" t="s">
         <v>1365</v>
@@ -21793,15 +21786,15 @@
       </c>
       <c r="F510" s="19"/>
       <c r="G510" s="2" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A511" s="6" t="s">
         <v>1662</v>
       </c>
-    </row>
-    <row r="511" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A511" s="6" t="s">
+      <c r="B511" s="6" t="s">
         <v>1663</v>
-      </c>
-      <c r="B511" s="6" t="s">
-        <v>1664</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>1365</v>
@@ -21816,15 +21809,15 @@
         <v>1000000</v>
       </c>
       <c r="G511" s="2" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A512" s="6" t="s">
         <v>1665</v>
       </c>
-    </row>
-    <row r="512" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A512" s="6" t="s">
+      <c r="B512" s="6" t="s">
         <v>1666</v>
-      </c>
-      <c r="B512" s="6" t="s">
-        <v>1667</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>1365</v>
@@ -21837,15 +21830,15 @@
       </c>
       <c r="F512" s="19"/>
       <c r="G512" s="2" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A513" s="6" t="s">
         <v>1668</v>
       </c>
-    </row>
-    <row r="513" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A513" s="6" t="s">
+      <c r="B513" s="6" t="s">
         <v>1669</v>
-      </c>
-      <c r="B513" s="6" t="s">
-        <v>1670</v>
       </c>
       <c r="C513" s="1" t="s">
         <v>1365</v>
@@ -21860,15 +21853,15 @@
         <v>2000000</v>
       </c>
       <c r="G513" s="2" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A514" s="6" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="514" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A514" s="6" t="s">
+      <c r="B514" s="6" t="s">
         <v>1672</v>
-      </c>
-      <c r="B514" s="6" t="s">
-        <v>1673</v>
       </c>
       <c r="C514" s="1" t="s">
         <v>1365</v>
@@ -21883,15 +21876,15 @@
         <v>1000000</v>
       </c>
       <c r="G514" s="2" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A515" s="6" t="s">
         <v>1674</v>
       </c>
-    </row>
-    <row r="515" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A515" s="6" t="s">
+      <c r="B515" s="6" t="s">
         <v>1675</v>
-      </c>
-      <c r="B515" s="6" t="s">
-        <v>1676</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>1365</v>
@@ -21906,15 +21899,15 @@
         <v>1000000</v>
       </c>
       <c r="G515" s="2" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A516" s="6" t="s">
         <v>1677</v>
       </c>
-    </row>
-    <row r="516" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A516" s="6" t="s">
+      <c r="B516" s="6" t="s">
         <v>1678</v>
-      </c>
-      <c r="B516" s="6" t="s">
-        <v>1679</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>1365</v>
@@ -21929,15 +21922,15 @@
         <v>840000</v>
       </c>
       <c r="G516" s="2" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A517" s="6" t="s">
         <v>1680</v>
       </c>
-    </row>
-    <row r="517" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A517" s="6" t="s">
+      <c r="B517" s="6" t="s">
         <v>1681</v>
-      </c>
-      <c r="B517" s="6" t="s">
-        <v>1682</v>
       </c>
       <c r="C517" s="1" t="s">
         <v>1365</v>
@@ -21950,15 +21943,15 @@
       </c>
       <c r="F517" s="19"/>
       <c r="G517" s="2" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A518" s="6" t="s">
         <v>1683</v>
       </c>
-    </row>
-    <row r="518" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A518" s="6" t="s">
+      <c r="B518" s="6" t="s">
         <v>1684</v>
-      </c>
-      <c r="B518" s="6" t="s">
-        <v>1685</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>1365</v>
@@ -21973,15 +21966,15 @@
         <v>1000000</v>
       </c>
       <c r="G518" s="2" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A519" s="6" t="s">
         <v>1686</v>
       </c>
-    </row>
-    <row r="519" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A519" s="6" t="s">
+      <c r="B519" s="6" t="s">
         <v>1687</v>
-      </c>
-      <c r="B519" s="6" t="s">
-        <v>1688</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>1365</v>
@@ -21996,15 +21989,15 @@
         <v>1000000</v>
       </c>
       <c r="G519" s="2" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A520" s="6" t="s">
         <v>1689</v>
       </c>
-    </row>
-    <row r="520" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A520" s="6" t="s">
+      <c r="B520" s="6" t="s">
         <v>1690</v>
-      </c>
-      <c r="B520" s="6" t="s">
-        <v>1691</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>1365</v>
@@ -22017,15 +22010,15 @@
       </c>
       <c r="F520" s="19"/>
       <c r="G520" s="2" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A521" s="6" t="s">
         <v>1692</v>
       </c>
-    </row>
-    <row r="521" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A521" s="6" t="s">
+      <c r="B521" s="6" t="s">
         <v>1693</v>
-      </c>
-      <c r="B521" s="6" t="s">
-        <v>1694</v>
       </c>
       <c r="C521" s="1" t="s">
         <v>1365</v>
@@ -22038,15 +22031,15 @@
       </c>
       <c r="F521" s="19"/>
       <c r="G521" s="2" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A522" s="6" t="s">
         <v>1695</v>
       </c>
-    </row>
-    <row r="522" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A522" s="6" t="s">
+      <c r="B522" s="6" t="s">
         <v>1696</v>
-      </c>
-      <c r="B522" s="6" t="s">
-        <v>1697</v>
       </c>
       <c r="C522" s="1" t="s">
         <v>1365</v>
@@ -22061,15 +22054,15 @@
         <v>2000000</v>
       </c>
       <c r="G522" s="2" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A523" s="6" t="s">
         <v>1698</v>
       </c>
-    </row>
-    <row r="523" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A523" s="6" t="s">
+      <c r="B523" s="6" t="s">
         <v>1699</v>
-      </c>
-      <c r="B523" s="6" t="s">
-        <v>1700</v>
       </c>
       <c r="C523" s="1" t="s">
         <v>1365</v>
@@ -22084,15 +22077,15 @@
         <v>5000000</v>
       </c>
       <c r="G523" s="2" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A524" s="6" t="s">
         <v>1701</v>
       </c>
-    </row>
-    <row r="524" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A524" s="6" t="s">
+      <c r="B524" s="6" t="s">
         <v>1702</v>
-      </c>
-      <c r="B524" s="6" t="s">
-        <v>1703</v>
       </c>
       <c r="C524" s="1" t="s">
         <v>1365</v>
@@ -22105,15 +22098,15 @@
       </c>
       <c r="F524" s="19"/>
       <c r="G524" s="2" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A525" s="6" t="s">
         <v>1704</v>
       </c>
-    </row>
-    <row r="525" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A525" s="6" t="s">
-        <v>1705</v>
-      </c>
       <c r="B525" s="6" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C525" s="1" t="s">
         <v>1365</v>
@@ -22126,15 +22119,15 @@
       </c>
       <c r="F525" s="19"/>
       <c r="G525" s="2" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A526" s="6" t="s">
         <v>1706</v>
       </c>
-    </row>
-    <row r="526" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A526" s="6" t="s">
-        <v>1707</v>
-      </c>
       <c r="B526" s="6" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C526" s="1" t="s">
         <v>1365</v>
@@ -22147,15 +22140,15 @@
       </c>
       <c r="F526" s="19"/>
       <c r="G526" s="2" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A527" s="6" t="s">
         <v>1708</v>
       </c>
-    </row>
-    <row r="527" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A527" s="6" t="s">
-        <v>1709</v>
-      </c>
       <c r="B527" s="6" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C527" s="1" t="s">
         <v>1365</v>
@@ -22168,15 +22161,15 @@
       </c>
       <c r="F527" s="19"/>
       <c r="G527" s="2" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A528" s="6" t="s">
         <v>1710</v>
       </c>
-    </row>
-    <row r="528" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A528" s="6" t="s">
+      <c r="B528" s="6" t="s">
         <v>1711</v>
-      </c>
-      <c r="B528" s="6" t="s">
-        <v>1712</v>
       </c>
       <c r="C528" s="1" t="s">
         <v>1365</v>
@@ -22191,15 +22184,15 @@
         <v>1000000</v>
       </c>
       <c r="G528" s="2" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A529" s="6" t="s">
         <v>1713</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A529" s="6" t="s">
+      <c r="B529" s="6" t="s">
         <v>1714</v>
-      </c>
-      <c r="B529" s="6" t="s">
-        <v>1715</v>
       </c>
       <c r="C529" s="1" t="s">
         <v>1365</v>
@@ -22214,15 +22207,15 @@
         <v>1000000</v>
       </c>
       <c r="G529" s="2" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A530" s="6" t="s">
         <v>1716</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A530" s="6" t="s">
+      <c r="B530" s="6" t="s">
         <v>1717</v>
-      </c>
-      <c r="B530" s="6" t="s">
-        <v>1718</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>1365</v>
@@ -22237,15 +22230,15 @@
         <v>500000</v>
       </c>
       <c r="G530" s="2" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A531" s="6" t="s">
         <v>1719</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A531" s="6" t="s">
+      <c r="B531" s="6" t="s">
         <v>1720</v>
-      </c>
-      <c r="B531" s="6" t="s">
-        <v>1721</v>
       </c>
       <c r="C531" s="1" t="s">
         <v>1365</v>
@@ -22260,15 +22253,15 @@
         <v>500000</v>
       </c>
       <c r="G531" s="2" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A532" s="6" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A532" s="6" t="s">
+      <c r="B532" s="6" t="s">
         <v>1723</v>
-      </c>
-      <c r="B532" s="6" t="s">
-        <v>1724</v>
       </c>
       <c r="C532" s="1" t="s">
         <v>1365</v>
@@ -22283,15 +22276,15 @@
         <v>3000000</v>
       </c>
       <c r="G532" s="2" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A533" s="6" t="s">
         <v>1725</v>
       </c>
-    </row>
-    <row r="533" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A533" s="6" t="s">
+      <c r="B533" s="6" t="s">
         <v>1726</v>
-      </c>
-      <c r="B533" s="6" t="s">
-        <v>1727</v>
       </c>
       <c r="C533" s="1" t="s">
         <v>1365</v>
@@ -22306,15 +22299,15 @@
         <v>1000000</v>
       </c>
       <c r="G533" s="2" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A534" s="6" t="s">
         <v>1728</v>
       </c>
-    </row>
-    <row r="534" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A534" s="6" t="s">
+      <c r="B534" s="6" t="s">
         <v>1729</v>
-      </c>
-      <c r="B534" s="6" t="s">
-        <v>1730</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>1365</v>
@@ -22327,15 +22320,15 @@
       </c>
       <c r="F534" s="19"/>
       <c r="G534" s="2" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A535" s="6" t="s">
         <v>1731</v>
       </c>
-    </row>
-    <row r="535" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A535" s="6" t="s">
+      <c r="B535" s="6" t="s">
         <v>1732</v>
-      </c>
-      <c r="B535" s="6" t="s">
-        <v>1733</v>
       </c>
       <c r="C535" s="1" t="s">
         <v>1365</v>
@@ -22350,15 +22343,15 @@
         <v>1000000</v>
       </c>
       <c r="G535" s="2" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A536" s="6" t="s">
         <v>1734</v>
       </c>
-    </row>
-    <row r="536" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A536" s="6" t="s">
+      <c r="B536" s="6" t="s">
         <v>1735</v>
-      </c>
-      <c r="B536" s="6" t="s">
-        <v>1736</v>
       </c>
       <c r="C536" s="1" t="s">
         <v>1365</v>
@@ -22373,15 +22366,15 @@
         <v>1000000</v>
       </c>
       <c r="G536" s="2" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A537" s="6" t="s">
         <v>1737</v>
       </c>
-    </row>
-    <row r="537" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A537" s="6" t="s">
+      <c r="B537" s="6" t="s">
         <v>1738</v>
-      </c>
-      <c r="B537" s="6" t="s">
-        <v>1739</v>
       </c>
       <c r="C537" s="1" t="s">
         <v>1365</v>
@@ -22394,15 +22387,15 @@
       </c>
       <c r="F537" s="19"/>
       <c r="G537" s="2" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A538" s="6" t="s">
         <v>1740</v>
       </c>
-    </row>
-    <row r="538" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A538" s="6" t="s">
+      <c r="B538" s="6" t="s">
         <v>1741</v>
-      </c>
-      <c r="B538" s="6" t="s">
-        <v>1742</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>1365</v>
@@ -22417,12 +22410,12 @@
         <v>1000000</v>
       </c>
       <c r="G538" s="2" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A539" s="6" t="s">
         <v>1743</v>
-      </c>
-    </row>
-    <row r="539" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A539" s="6" t="s">
-        <v>1744</v>
       </c>
       <c r="B539" s="6" t="s">
         <v>1510</v>
@@ -22440,21 +22433,21 @@
         <v>1000000</v>
       </c>
       <c r="G539" s="2" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A540" s="6" t="s">
         <v>1745</v>
       </c>
-    </row>
-    <row r="540" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A540" s="6" t="s">
+      <c r="B540" s="6" t="s">
         <v>1746</v>
       </c>
-      <c r="B540" s="6" t="s">
+      <c r="C540" s="1" t="s">
         <v>1747</v>
       </c>
-      <c r="C540" s="1" t="s">
+      <c r="D540" s="1" t="s">
         <v>1748</v>
-      </c>
-      <c r="D540" s="1" t="s">
-        <v>1749</v>
       </c>
       <c r="E540" s="11">
         <v>1400000</v>
@@ -22463,21 +22456,21 @@
         <v>500000</v>
       </c>
       <c r="G540" s="2" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A541" s="6" t="s">
         <v>1750</v>
       </c>
-    </row>
-    <row r="541" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A541" s="6" t="s">
+      <c r="B541" s="6" t="s">
         <v>1751</v>
       </c>
-      <c r="B541" s="6" t="s">
+      <c r="C541" s="1" t="s">
         <v>1752</v>
       </c>
-      <c r="C541" s="1" t="s">
+      <c r="D541" s="1" t="s">
         <v>1753</v>
-      </c>
-      <c r="D541" s="1" t="s">
-        <v>1754</v>
       </c>
       <c r="E541" s="11">
         <v>3000000</v>
@@ -22486,18 +22479,18 @@
         <v>1500000</v>
       </c>
       <c r="G541" s="2" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A542" s="6" t="s">
         <v>1755</v>
       </c>
-    </row>
-    <row r="542" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A542" s="6" t="s">
+      <c r="B542" s="6" t="s">
         <v>1756</v>
       </c>
-      <c r="B542" s="6" t="s">
-        <v>1757</v>
-      </c>
       <c r="C542" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="D542" s="1" t="s">
         <v>105</v>
@@ -22509,21 +22502,21 @@
         <v>2500000</v>
       </c>
       <c r="G542" s="2" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A543" s="6" t="s">
         <v>1758</v>
       </c>
-    </row>
-    <row r="543" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A543" s="6" t="s">
+      <c r="B543" s="6" t="s">
         <v>1759</v>
       </c>
-      <c r="B543" s="6" t="s">
+      <c r="C543" s="1" t="s">
         <v>1760</v>
       </c>
-      <c r="C543" s="1" t="s">
+      <c r="D543" s="1" t="s">
         <v>1761</v>
-      </c>
-      <c r="D543" s="1" t="s">
-        <v>1762</v>
       </c>
       <c r="E543" s="11">
         <v>500000</v>
@@ -22532,21 +22525,21 @@
         <v>500000</v>
       </c>
       <c r="G543" s="2" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A544" s="6" t="s">
         <v>1763</v>
       </c>
-    </row>
-    <row r="544" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A544" s="6" t="s">
+      <c r="B544" s="6" t="s">
         <v>1764</v>
       </c>
-      <c r="B544" s="6" t="s">
+      <c r="C544" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D544" s="1" t="s">
         <v>1765</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D544" s="1" t="s">
-        <v>1766</v>
       </c>
       <c r="E544" s="11">
         <v>500000</v>
@@ -22555,21 +22548,21 @@
         <v>250000</v>
       </c>
       <c r="G544" s="2" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A545" s="6" t="s">
         <v>1767</v>
       </c>
-    </row>
-    <row r="545" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A545" s="6" t="s">
+      <c r="B545" s="6" t="s">
         <v>1768</v>
       </c>
-      <c r="B545" s="6" t="s">
+      <c r="C545" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D545" s="1" t="s">
         <v>1769</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D545" s="1" t="s">
-        <v>1770</v>
       </c>
       <c r="E545" s="11">
         <v>500000</v>
@@ -22578,42 +22571,42 @@
         <v>500000</v>
       </c>
       <c r="G545" s="2" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A546" s="6" t="s">
         <v>1771</v>
       </c>
-    </row>
-    <row r="546" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A546" s="6" t="s">
+      <c r="B546" s="6" t="s">
         <v>1772</v>
       </c>
-      <c r="B546" s="6" t="s">
+      <c r="C546" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D546" s="1" t="s">
         <v>1773</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D546" s="1" t="s">
-        <v>1774</v>
       </c>
       <c r="E546" s="11">
         <v>579392</v>
       </c>
       <c r="F546" s="19"/>
       <c r="G546" s="2" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A547" s="6" t="s">
         <v>1775</v>
       </c>
-    </row>
-    <row r="547" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A547" s="6" t="s">
+      <c r="B547" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="B547" s="6" t="s">
+      <c r="C547" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D547" s="1" t="s">
         <v>1777</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D547" s="1" t="s">
-        <v>1778</v>
       </c>
       <c r="E547" s="11">
         <v>1000000</v>
@@ -22622,42 +22615,42 @@
         <v>1000000</v>
       </c>
       <c r="G547" s="2" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A548" s="6" t="s">
         <v>1779</v>
       </c>
-    </row>
-    <row r="548" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A548" s="6" t="s">
+      <c r="B548" s="6" t="s">
         <v>1780</v>
       </c>
-      <c r="B548" s="6" t="s">
+      <c r="C548" s="1" t="s">
         <v>1781</v>
       </c>
-      <c r="C548" s="1" t="s">
+      <c r="D548" s="1" t="s">
         <v>1782</v>
-      </c>
-      <c r="D548" s="1" t="s">
-        <v>1783</v>
       </c>
       <c r="E548" s="11">
         <v>3000000</v>
       </c>
       <c r="F548" s="19"/>
       <c r="G548" s="2" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A549" s="6" t="s">
         <v>1784</v>
       </c>
-    </row>
-    <row r="549" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A549" s="6" t="s">
+      <c r="B549" s="6" t="s">
         <v>1785</v>
       </c>
-      <c r="B549" s="6" t="s">
+      <c r="C549" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D549" s="1" t="s">
         <v>1786</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>1782</v>
-      </c>
-      <c r="D549" s="1" t="s">
-        <v>1787</v>
       </c>
       <c r="E549" s="11">
         <v>4800000</v>
@@ -22666,42 +22659,42 @@
         <v>2000000</v>
       </c>
       <c r="G549" s="2" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A550" s="6" t="s">
         <v>1788</v>
       </c>
-    </row>
-    <row r="550" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A550" s="6" t="s">
+      <c r="B550" s="6" t="s">
         <v>1789</v>
       </c>
-      <c r="B550" s="6" t="s">
+      <c r="C550" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="C550" s="1" t="s">
+      <c r="D550" s="1" t="s">
         <v>1791</v>
-      </c>
-      <c r="D550" s="1" t="s">
-        <v>1792</v>
       </c>
       <c r="E550" s="11">
         <v>1500000</v>
       </c>
       <c r="F550" s="19"/>
       <c r="G550" s="2" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A551" s="6" t="s">
         <v>1793</v>
       </c>
-    </row>
-    <row r="551" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A551" s="6" t="s">
+      <c r="B551" s="6" t="s">
         <v>1794</v>
       </c>
-      <c r="B551" s="6" t="s">
+      <c r="C551" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D551" s="1" t="s">
         <v>1795</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D551" s="1" t="s">
-        <v>1796</v>
       </c>
       <c r="E551" s="11">
         <v>7462353</v>
@@ -22710,63 +22703,63 @@
         <v>2000000</v>
       </c>
       <c r="G551" s="2" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A552" s="6" t="s">
         <v>1797</v>
       </c>
-    </row>
-    <row r="552" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A552" s="6" t="s">
+      <c r="B552" s="6" t="s">
         <v>1798</v>
       </c>
-      <c r="B552" s="6" t="s">
+      <c r="C552" s="1" t="s">
         <v>1799</v>
       </c>
-      <c r="C552" s="1" t="s">
+      <c r="D552" s="1" t="s">
         <v>1800</v>
-      </c>
-      <c r="D552" s="1" t="s">
-        <v>1801</v>
       </c>
       <c r="E552" s="11">
         <v>2150000</v>
       </c>
       <c r="F552" s="19"/>
       <c r="G552" s="2" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A553" s="6" t="s">
         <v>1802</v>
       </c>
-    </row>
-    <row r="553" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A553" s="6" t="s">
+      <c r="B553" s="6" t="s">
         <v>1803</v>
       </c>
-      <c r="B553" s="6" t="s">
+      <c r="C553" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D553" s="1" t="s">
         <v>1804</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D553" s="1" t="s">
-        <v>1805</v>
       </c>
       <c r="E553" s="11">
         <v>900000</v>
       </c>
       <c r="F553" s="19"/>
       <c r="G553" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A554" s="6" t="s">
         <v>1806</v>
       </c>
-    </row>
-    <row r="554" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A554" s="6" t="s">
+      <c r="B554" s="6" t="s">
         <v>1807</v>
       </c>
-      <c r="B554" s="6" t="s">
+      <c r="C554" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="C554" s="1" t="s">
+      <c r="D554" s="1" t="s">
         <v>1809</v>
-      </c>
-      <c r="D554" s="1" t="s">
-        <v>1810</v>
       </c>
       <c r="E554" s="11">
         <v>4600000</v>
@@ -22775,21 +22768,21 @@
         <v>2000000</v>
       </c>
       <c r="G554" s="2" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A555" s="6" t="s">
         <v>1811</v>
       </c>
-    </row>
-    <row r="555" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A555" s="6" t="s">
+      <c r="B555" s="6" t="s">
         <v>1812</v>
       </c>
-      <c r="B555" s="6" t="s">
+      <c r="C555" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D555" s="1" t="s">
         <v>1813</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D555" s="1" t="s">
-        <v>1814</v>
       </c>
       <c r="E555" s="11">
         <v>1500000</v>
@@ -22798,21 +22791,21 @@
         <v>1500000</v>
       </c>
       <c r="G555" s="2" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A556" s="6" t="s">
         <v>1815</v>
       </c>
-    </row>
-    <row r="556" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A556" s="6" t="s">
+      <c r="B556" s="6" t="s">
         <v>1816</v>
       </c>
-      <c r="B556" s="6" t="s">
-        <v>1817</v>
-      </c>
       <c r="C556" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D556" s="1" t="s">
         <v>1809</v>
-      </c>
-      <c r="D556" s="1" t="s">
-        <v>1810</v>
       </c>
       <c r="E556" s="11">
         <v>2000000</v>
@@ -22821,18 +22814,18 @@
         <v>750000</v>
       </c>
       <c r="G556" s="2" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A557" s="6" t="s">
         <v>1818</v>
       </c>
-    </row>
-    <row r="557" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A557" s="6" t="s">
+      <c r="B557" s="6" t="s">
         <v>1819</v>
       </c>
-      <c r="B557" s="6" t="s">
+      <c r="C557" s="1" t="s">
         <v>1820</v>
-      </c>
-      <c r="C557" s="1" t="s">
-        <v>1821</v>
       </c>
       <c r="D557" s="1" t="s">
         <v>93</v>
@@ -22844,42 +22837,42 @@
         <v>1000000</v>
       </c>
       <c r="G557" s="2" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A558" s="6" t="s">
         <v>1822</v>
       </c>
-    </row>
-    <row r="558" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A558" s="6" t="s">
+      <c r="B558" s="6" t="s">
         <v>1823</v>
       </c>
-      <c r="B558" s="6" t="s">
+      <c r="C558" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D558" s="1" t="s">
         <v>1824</v>
-      </c>
-      <c r="C558" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D558" s="1" t="s">
-        <v>1825</v>
       </c>
       <c r="E558" s="11">
         <v>750000</v>
       </c>
       <c r="F558" s="19"/>
       <c r="G558" s="2" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A559" s="6" t="s">
         <v>1826</v>
       </c>
-    </row>
-    <row r="559" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A559" s="6" t="s">
+      <c r="B559" s="6" t="s">
         <v>1827</v>
       </c>
-      <c r="B559" s="6" t="s">
+      <c r="C559" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1828</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1829</v>
       </c>
       <c r="E559" s="11">
         <v>500000</v>
@@ -22888,21 +22881,21 @@
         <v>500000</v>
       </c>
       <c r="G559" s="2" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A560" s="6" t="s">
         <v>1830</v>
       </c>
-    </row>
-    <row r="560" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A560" s="6" t="s">
+      <c r="B560" s="6" t="s">
         <v>1831</v>
       </c>
-      <c r="B560" s="6" t="s">
+      <c r="C560" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D560" s="1" t="s">
         <v>1832</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D560" s="1" t="s">
-        <v>1833</v>
       </c>
       <c r="E560" s="11">
         <v>1066625</v>
@@ -22911,63 +22904,63 @@
         <v>841000</v>
       </c>
       <c r="G560" s="2" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A561" s="6" t="s">
         <v>1834</v>
       </c>
-    </row>
-    <row r="561" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A561" s="6" t="s">
+      <c r="B561" s="6" t="s">
         <v>1835</v>
       </c>
-      <c r="B561" s="6" t="s">
-        <v>1836</v>
-      </c>
       <c r="C561" s="1" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E561" s="11">
         <v>5411829</v>
       </c>
       <c r="F561" s="19"/>
       <c r="G561" s="2" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A562" s="6" t="s">
         <v>1837</v>
       </c>
-    </row>
-    <row r="562" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A562" s="6" t="s">
-        <v>1838</v>
-      </c>
       <c r="B562" s="6" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E562" s="11">
         <v>4097780</v>
       </c>
       <c r="F562" s="19"/>
       <c r="G562" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A563" s="6" t="s">
         <v>1839</v>
       </c>
-    </row>
-    <row r="563" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A563" s="6" t="s">
+      <c r="B563" s="6" t="s">
         <v>1840</v>
       </c>
-      <c r="B563" s="6" t="s">
+      <c r="C563" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D563" s="1" t="s">
         <v>1841</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D563" s="1" t="s">
-        <v>1842</v>
       </c>
       <c r="E563" s="11">
         <v>8000000</v>
@@ -22976,18 +22969,18 @@
         <v>1500000</v>
       </c>
       <c r="G563" s="2" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A564" s="6" t="s">
         <v>1843</v>
       </c>
-    </row>
-    <row r="564" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A564" s="6" t="s">
+      <c r="B564" s="6" t="s">
         <v>1844</v>
       </c>
-      <c r="B564" s="6" t="s">
-        <v>1845</v>
-      </c>
       <c r="C564" s="1" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="D564" s="1" t="s">
         <v>93</v>
@@ -22999,21 +22992,21 @@
         <v>500000</v>
       </c>
       <c r="G564" s="2" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A565" s="6" t="s">
         <v>1846</v>
       </c>
-    </row>
-    <row r="565" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A565" s="6" t="s">
+      <c r="B565" s="6" t="s">
         <v>1847</v>
       </c>
-      <c r="B565" s="6" t="s">
+      <c r="C565" s="1" t="s">
         <v>1848</v>
       </c>
-      <c r="C565" s="1" t="s">
+      <c r="D565" s="1" t="s">
         <v>1849</v>
-      </c>
-      <c r="D565" s="1" t="s">
-        <v>1850</v>
       </c>
       <c r="E565" s="11">
         <v>1000000</v>
@@ -23022,21 +23015,21 @@
         <v>1000000</v>
       </c>
       <c r="G565" s="2" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A566" s="6" t="s">
         <v>1851</v>
       </c>
-    </row>
-    <row r="566" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A566" s="6" t="s">
+      <c r="B566" s="6" t="s">
         <v>1852</v>
       </c>
-      <c r="B566" s="6" t="s">
+      <c r="C566" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D566" s="1" t="s">
         <v>1853</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D566" s="1" t="s">
-        <v>1854</v>
       </c>
       <c r="E566" s="11">
         <v>2431922</v>
@@ -23045,21 +23038,21 @@
         <v>1000000</v>
       </c>
       <c r="G566" s="2" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A567" s="6" t="s">
         <v>1855</v>
       </c>
-    </row>
-    <row r="567" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A567" s="6" t="s">
+      <c r="B567" s="6" t="s">
         <v>1856</v>
       </c>
-      <c r="B567" s="6" t="s">
+      <c r="C567" s="1" t="s">
         <v>1857</v>
       </c>
-      <c r="C567" s="1" t="s">
+      <c r="D567" s="1" t="s">
         <v>1858</v>
-      </c>
-      <c r="D567" s="1" t="s">
-        <v>1859</v>
       </c>
       <c r="E567" s="11">
         <v>2000000</v>
@@ -23068,21 +23061,21 @@
         <v>750000</v>
       </c>
       <c r="G567" s="2" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A568" s="6" t="s">
         <v>1860</v>
       </c>
-    </row>
-    <row r="568" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A568" s="6" t="s">
+      <c r="B568" s="6" t="s">
         <v>1861</v>
       </c>
-      <c r="B568" s="6" t="s">
+      <c r="C568" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D568" s="1" t="s">
         <v>1862</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D568" s="1" t="s">
-        <v>1863</v>
       </c>
       <c r="E568" s="11">
         <v>2789781</v>
@@ -23091,21 +23084,21 @@
         <v>700000</v>
       </c>
       <c r="G568" s="2" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A569" s="6" t="s">
         <v>1864</v>
       </c>
-    </row>
-    <row r="569" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A569" s="6" t="s">
+      <c r="B569" s="6" t="s">
         <v>1865</v>
       </c>
-      <c r="B569" s="6" t="s">
+      <c r="C569" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D569" s="1" t="s">
         <v>1866</v>
-      </c>
-      <c r="C569" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D569" s="1" t="s">
-        <v>1867</v>
       </c>
       <c r="E569" s="11">
         <v>1500000</v>
@@ -23114,42 +23107,42 @@
         <v>1250000</v>
       </c>
       <c r="G569" s="2" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A570" s="6" t="s">
         <v>1868</v>
       </c>
-    </row>
-    <row r="570" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A570" s="6" t="s">
+      <c r="B570" s="6" t="s">
         <v>1869</v>
       </c>
-      <c r="B570" s="6" t="s">
-        <v>1870</v>
-      </c>
       <c r="C570" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D570" s="1" t="s">
         <v>1858</v>
-      </c>
-      <c r="D570" s="1" t="s">
-        <v>1859</v>
       </c>
       <c r="E570" s="11">
         <v>3500000</v>
       </c>
       <c r="F570" s="19"/>
       <c r="G570" s="2" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A571" s="6" t="s">
         <v>1871</v>
       </c>
-    </row>
-    <row r="571" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A571" s="6" t="s">
+      <c r="B571" s="6" t="s">
         <v>1872</v>
       </c>
-      <c r="B571" s="6" t="s">
+      <c r="C571" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D571" s="1" t="s">
         <v>1873</v>
-      </c>
-      <c r="C571" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D571" s="1" t="s">
-        <v>1874</v>
       </c>
       <c r="E571" s="11">
         <v>5000000</v>
@@ -23158,21 +23151,21 @@
         <v>1000000</v>
       </c>
       <c r="G571" s="2" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A572" s="6" t="s">
         <v>1875</v>
       </c>
-    </row>
-    <row r="572" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A572" s="6" t="s">
+      <c r="B572" s="6" t="s">
         <v>1876</v>
       </c>
-      <c r="B572" s="6" t="s">
-        <v>1877</v>
-      </c>
       <c r="C572" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="E572" s="11">
         <v>5000000</v>
@@ -23181,21 +23174,21 @@
         <v>1500000</v>
       </c>
       <c r="G572" s="2" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A573" s="6" t="s">
         <v>1878</v>
       </c>
-    </row>
-    <row r="573" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A573" s="6" t="s">
+      <c r="B573" s="6" t="s">
         <v>1879</v>
       </c>
-      <c r="B573" s="6" t="s">
+      <c r="C573" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D573" s="1" t="s">
         <v>1880</v>
-      </c>
-      <c r="C573" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>1881</v>
       </c>
       <c r="E573" s="11">
         <v>2000000</v>
@@ -23204,60 +23197,60 @@
         <v>500000</v>
       </c>
       <c r="G573" s="2" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A574" s="6" t="s">
         <v>1882</v>
       </c>
-    </row>
-    <row r="574" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A574" s="6" t="s">
+      <c r="B574" s="6" t="s">
         <v>1883</v>
       </c>
-      <c r="B574" s="6" t="s">
+      <c r="C574" s="1" t="s">
         <v>1884</v>
       </c>
-      <c r="C574" s="1" t="s">
+      <c r="D574" s="1" t="s">
         <v>1885</v>
-      </c>
-      <c r="D574" s="1" t="s">
-        <v>1886</v>
       </c>
       <c r="E574" s="11">
         <v>500000</v>
       </c>
       <c r="F574" s="19"/>
       <c r="G574" s="2" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A575" s="6" t="s">
         <v>1887</v>
       </c>
-    </row>
-    <row r="575" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A575" s="6" t="s">
+      <c r="B575" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="B575" s="6" t="s">
+      <c r="C575" s="1" t="s">
         <v>1889</v>
       </c>
-      <c r="C575" s="1" t="s">
+      <c r="D575" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D575" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E575" s="11">
         <v>1374000</v>
       </c>
       <c r="F575" s="19"/>
       <c r="G575" s="2" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A576" s="6" t="s">
         <v>1892</v>
       </c>
-    </row>
-    <row r="576" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A576" s="6" t="s">
+      <c r="B576" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="B576" s="6" t="s">
-        <v>1894</v>
-      </c>
       <c r="C576" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D576" s="1" t="s">
         <v>1103</v>
@@ -23267,21 +23260,21 @@
       </c>
       <c r="F576" s="19"/>
       <c r="G576" s="2" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A577" s="6" t="s">
         <v>1895</v>
       </c>
-    </row>
-    <row r="577" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A577" s="6" t="s">
+      <c r="B577" s="6" t="s">
         <v>1896</v>
       </c>
-      <c r="B577" s="6" t="s">
-        <v>1897</v>
-      </c>
       <c r="C577" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D577" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D577" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E577" s="11">
         <v>1000000</v>
@@ -23290,42 +23283,42 @@
         <v>1000000</v>
       </c>
       <c r="G577" s="2" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A578" s="6" t="s">
         <v>1898</v>
       </c>
-    </row>
-    <row r="578" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A578" s="6" t="s">
+      <c r="B578" s="6" t="s">
         <v>1899</v>
       </c>
-      <c r="B578" s="6" t="s">
-        <v>1900</v>
-      </c>
       <c r="C578" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D578" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D578" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E578" s="11">
         <v>3000000</v>
       </c>
       <c r="F578" s="19"/>
       <c r="G578" s="2" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A579" s="6" t="s">
         <v>1901</v>
       </c>
-    </row>
-    <row r="579" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A579" s="6" t="s">
+      <c r="B579" s="6" t="s">
         <v>1902</v>
       </c>
-      <c r="B579" s="6" t="s">
+      <c r="C579" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D579" s="1" t="s">
         <v>1903</v>
-      </c>
-      <c r="C579" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D579" s="1" t="s">
-        <v>1904</v>
       </c>
       <c r="E579" s="11">
         <v>670000</v>
@@ -23334,63 +23327,63 @@
         <v>500000</v>
       </c>
       <c r="G579" s="2" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A580" s="6" t="s">
         <v>1905</v>
       </c>
-    </row>
-    <row r="580" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A580" s="6" t="s">
-        <v>1906</v>
-      </c>
       <c r="B580" s="6" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="C580" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D580" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D580" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E580" s="11">
         <v>3257753</v>
       </c>
       <c r="F580" s="19"/>
       <c r="G580" s="2" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A581" s="6" t="s">
         <v>1907</v>
       </c>
-    </row>
-    <row r="581" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A581" s="6" t="s">
+      <c r="B581" s="6" t="s">
         <v>1908</v>
       </c>
-      <c r="B581" s="6" t="s">
-        <v>1909</v>
-      </c>
       <c r="C581" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D581" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D581" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E581" s="11">
         <v>3000000</v>
       </c>
       <c r="F581" s="19"/>
       <c r="G581" s="2" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A582" s="6" t="s">
         <v>1910</v>
       </c>
-    </row>
-    <row r="582" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A582" s="6" t="s">
+      <c r="B582" s="6" t="s">
         <v>1911</v>
       </c>
-      <c r="B582" s="6" t="s">
+      <c r="C582" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D582" s="1" t="s">
         <v>1912</v>
-      </c>
-      <c r="C582" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D582" s="1" t="s">
-        <v>1913</v>
       </c>
       <c r="E582" s="11">
         <v>1500000</v>
@@ -23399,21 +23392,21 @@
         <v>500000</v>
       </c>
       <c r="G582" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A583" s="6" t="s">
         <v>1914</v>
       </c>
-    </row>
-    <row r="583" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A583" s="6" t="s">
+      <c r="B583" s="6" t="s">
         <v>1915</v>
       </c>
-      <c r="B583" s="6" t="s">
-        <v>1916</v>
-      </c>
       <c r="C583" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E583" s="11">
         <v>1896000</v>
@@ -23422,21 +23415,21 @@
         <v>948000</v>
       </c>
       <c r="G583" s="2" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A584" s="6" t="s">
         <v>1917</v>
       </c>
-    </row>
-    <row r="584" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A584" s="6" t="s">
+      <c r="B584" s="6" t="s">
         <v>1918</v>
       </c>
-      <c r="B584" s="6" t="s">
-        <v>1919</v>
-      </c>
       <c r="C584" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D584" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D584" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E584" s="11">
         <v>3500000</v>
@@ -23445,21 +23438,21 @@
         <v>1500000</v>
       </c>
       <c r="G584" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A585" s="6" t="s">
         <v>1920</v>
       </c>
-    </row>
-    <row r="585" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A585" s="6" t="s">
+      <c r="B585" s="6" t="s">
         <v>1921</v>
       </c>
-      <c r="B585" s="6" t="s">
-        <v>1922</v>
-      </c>
       <c r="C585" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E585" s="11">
         <v>650000</v>
@@ -23468,21 +23461,21 @@
         <v>650000</v>
       </c>
       <c r="G585" s="2" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A586" s="6" t="s">
         <v>1923</v>
       </c>
-    </row>
-    <row r="586" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A586" s="6" t="s">
+      <c r="B586" s="6" t="s">
         <v>1924</v>
       </c>
-      <c r="B586" s="6" t="s">
+      <c r="C586" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D586" s="1" t="s">
         <v>1925</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>1926</v>
       </c>
       <c r="E586" s="11">
         <v>3000000</v>
@@ -23491,42 +23484,42 @@
         <v>1500000</v>
       </c>
       <c r="G586" s="2" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A587" s="6" t="s">
         <v>1927</v>
       </c>
-    </row>
-    <row r="587" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A587" s="6" t="s">
+      <c r="B587" s="6" t="s">
         <v>1928</v>
       </c>
-      <c r="B587" s="6" t="s">
-        <v>1929</v>
-      </c>
       <c r="C587" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D587" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D587" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E587" s="11">
         <v>6000000</v>
       </c>
       <c r="F587" s="19"/>
       <c r="G587" s="2" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A588" s="6" t="s">
         <v>1930</v>
       </c>
-    </row>
-    <row r="588" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A588" s="6" t="s">
+      <c r="B588" s="6" t="s">
         <v>1931</v>
       </c>
-      <c r="B588" s="6" t="s">
+      <c r="C588" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D588" s="1" t="s">
         <v>1932</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>1933</v>
       </c>
       <c r="E588" s="11">
         <v>525638</v>
@@ -23535,21 +23528,21 @@
         <v>525000</v>
       </c>
       <c r="G588" s="2" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A589" s="6" t="s">
         <v>1934</v>
       </c>
-    </row>
-    <row r="589" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A589" s="6" t="s">
+      <c r="B589" s="6" t="s">
         <v>1935</v>
       </c>
-      <c r="B589" s="6" t="s">
-        <v>1936</v>
-      </c>
       <c r="C589" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E589" s="11">
         <v>1419032</v>
@@ -23558,21 +23551,21 @@
         <v>1419032</v>
       </c>
       <c r="G589" s="2" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A590" s="6" t="s">
         <v>1937</v>
       </c>
-    </row>
-    <row r="590" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A590" s="6" t="s">
+      <c r="B590" s="6" t="s">
         <v>1938</v>
       </c>
-      <c r="B590" s="6" t="s">
-        <v>1939</v>
-      </c>
       <c r="C590" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D590" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D590" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E590" s="11">
         <v>1505000</v>
@@ -23581,84 +23574,84 @@
         <v>1500000</v>
       </c>
       <c r="G590" s="2" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A591" s="6" t="s">
         <v>1940</v>
       </c>
-    </row>
-    <row r="591" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A591" s="6" t="s">
+      <c r="B591" s="6" t="s">
         <v>1941</v>
       </c>
-      <c r="B591" s="6" t="s">
+      <c r="C591" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D591" s="1" t="s">
         <v>1942</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D591" s="1" t="s">
-        <v>1943</v>
       </c>
       <c r="E591" s="11">
         <v>4211685</v>
       </c>
       <c r="F591" s="19"/>
       <c r="G591" s="2" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A592" s="6" t="s">
         <v>1944</v>
       </c>
-    </row>
-    <row r="592" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A592" s="6" t="s">
+      <c r="B592" s="6" t="s">
         <v>1945</v>
       </c>
-      <c r="B592" s="6" t="s">
-        <v>1946</v>
-      </c>
       <c r="C592" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E592" s="11">
         <v>5000000</v>
       </c>
       <c r="F592" s="19"/>
       <c r="G592" s="2" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A593" s="6" t="s">
         <v>1947</v>
       </c>
-    </row>
-    <row r="593" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A593" s="6" t="s">
+      <c r="B593" s="6" t="s">
         <v>1948</v>
       </c>
-      <c r="B593" s="6" t="s">
-        <v>1949</v>
-      </c>
       <c r="C593" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D593" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D593" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E593" s="11">
         <v>2000000</v>
       </c>
       <c r="F593" s="19"/>
       <c r="G593" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A594" s="6" t="s">
         <v>1950</v>
       </c>
-    </row>
-    <row r="594" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A594" s="6" t="s">
+      <c r="B594" s="6" t="s">
         <v>1951</v>
       </c>
-      <c r="B594" s="6" t="s">
-        <v>1952</v>
-      </c>
       <c r="C594" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E594" s="11">
         <v>6200000</v>
@@ -23667,63 +23660,63 @@
         <v>1500000</v>
       </c>
       <c r="G594" s="2" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A595" s="6" t="s">
         <v>1953</v>
       </c>
-    </row>
-    <row r="595" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A595" s="6" t="s">
+      <c r="B595" s="6" t="s">
         <v>1954</v>
       </c>
-      <c r="B595" s="6" t="s">
-        <v>1955</v>
-      </c>
       <c r="C595" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D595" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E595" s="11">
         <v>5000000</v>
       </c>
       <c r="F595" s="19"/>
       <c r="G595" s="2" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A596" s="6" t="s">
         <v>1956</v>
       </c>
-    </row>
-    <row r="596" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A596" s="6" t="s">
+      <c r="B596" s="6" t="s">
         <v>1957</v>
       </c>
-      <c r="B596" s="6" t="s">
+      <c r="C596" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D596" s="1" t="s">
         <v>1958</v>
-      </c>
-      <c r="C596" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D596" s="1" t="s">
-        <v>1959</v>
       </c>
       <c r="E596" s="11">
         <v>5000000</v>
       </c>
       <c r="F596" s="19"/>
       <c r="G596" s="2" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" ht="102" x14ac:dyDescent="0.25">
+      <c r="A597" s="6" t="s">
         <v>1960</v>
       </c>
-    </row>
-    <row r="597" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A597" s="6" t="s">
+      <c r="B597" s="6" t="s">
         <v>1961</v>
       </c>
-      <c r="B597" s="6" t="s">
-        <v>1962</v>
-      </c>
       <c r="C597" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="E597" s="11">
         <v>3081000</v>
@@ -23732,63 +23725,63 @@
         <v>3081000</v>
       </c>
       <c r="G597" s="2" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A598" s="6" t="s">
         <v>1963</v>
       </c>
-    </row>
-    <row r="598" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A598" s="6" t="s">
+      <c r="B598" s="6" t="s">
         <v>1964</v>
       </c>
-      <c r="B598" s="6" t="s">
-        <v>1965</v>
-      </c>
       <c r="C598" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D598" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D598" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E598" s="11">
         <v>3000000</v>
       </c>
       <c r="F598" s="19"/>
       <c r="G598" s="2" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A599" s="6" t="s">
         <v>1966</v>
       </c>
-    </row>
-    <row r="599" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A599" s="6" t="s">
+      <c r="B599" s="6" t="s">
         <v>1967</v>
       </c>
-      <c r="B599" s="6" t="s">
-        <v>1968</v>
-      </c>
       <c r="C599" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D599" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D599" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E599" s="11">
         <v>1000000</v>
       </c>
       <c r="F599" s="19"/>
       <c r="G599" s="2" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A600" s="6" t="s">
         <v>1969</v>
       </c>
-    </row>
-    <row r="600" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A600" s="6" t="s">
+      <c r="B600" s="6" t="s">
         <v>1970</v>
       </c>
-      <c r="B600" s="6" t="s">
-        <v>1971</v>
-      </c>
       <c r="C600" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D600" s="1" t="s">
         <v>1890</v>
-      </c>
-      <c r="D600" s="1" t="s">
-        <v>1891</v>
       </c>
       <c r="E600" s="11">
         <v>1413826</v>
@@ -23797,13 +23790,13 @@
         <v>1413825</v>
       </c>
       <c r="G600" s="2" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E602" s="12"/>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E603" s="10"/>
     </row>
   </sheetData>
@@ -23817,6 +23810,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100420F3B8DD6992F4B9C1DE9DD96E4486F" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7ad8ec248fe312b9dc894641bff4c9fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="bfdc0969-8447-451b-99af-f83fc3c713f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a8c71706f1c6f62e424fe97951f1408" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -23973,25 +23984,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75DA519F-93AD-433A-B5AB-1E02A05E961B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C55DD6-54E6-430A-9F21-74A846B2ADA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47F43750-DCC1-40DB-93EF-E21A5A5C5BF1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24008,22 +24019,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C55DD6-54E6-430A-9F21-74A846B2ADA9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75DA519F-93AD-433A-B5AB-1E02A05E961B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>